--- a/out/thesis/tables/group_tests.xlsx
+++ b/out/thesis/tables/group_tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
   <si>
     <t>group_variable</t>
   </si>
@@ -52,10 +52,10 @@
     <t>RUNUP_PRE_30_5</t>
   </si>
   <si>
-    <t>BHAR_ANN_120</t>
-  </si>
-  <si>
-    <t>anova</t>
+    <t>kruskal_wallis</t>
+  </si>
+  <si>
+    <t>anova_f</t>
   </si>
 </sst>
 </file>
@@ -387,7 +387,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -418,13 +418,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>3.021638904653588</v>
+        <v>6.824139021857735</v>
       </c>
       <c r="E2">
-        <v>0.03240459426057671</v>
+        <v>0.07771938463324227</v>
       </c>
       <c r="F2">
         <v>4</v>
@@ -435,16 +435,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
       <c r="D3">
-        <v>2.212255031072405</v>
+        <v>3.04573876599705</v>
       </c>
       <c r="E3">
-        <v>0.09171062847104809</v>
+        <v>0.03142833400486504</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -455,19 +455,19 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>0.3753281453930475</v>
+        <v>3.071368335854142</v>
       </c>
       <c r="E4">
-        <v>0.7709499602123513</v>
+        <v>0.2153083337105105</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -475,59 +475,59 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0.5101593968029368</v>
+        <v>1.90213983253222</v>
       </c>
       <c r="E5">
-        <v>0.6759525606995871</v>
+        <v>0.155010164327115</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>1.133662157586463</v>
+        <v>2.15659883792379</v>
       </c>
       <c r="E6">
-        <v>0.3467334368563575</v>
+        <v>0.540547558427048</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7">
-        <v>0.6418200949062391</v>
+        <v>0.3752196583069287</v>
       </c>
       <c r="E7">
-        <v>0.6683926753614744</v>
+        <v>0.771028020631406</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -535,16 +535,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>1.118346817783894</v>
+        <v>4.833385244255167</v>
       </c>
       <c r="E8">
-        <v>0.354772773629875</v>
+        <v>0.4365508082721775</v>
       </c>
       <c r="F8">
         <v>6</v>
@@ -555,16 +555,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9">
-        <v>0.7077135529010028</v>
+        <v>1.130635936208173</v>
       </c>
       <c r="E9">
-        <v>0.6187129066959687</v>
+        <v>0.3482991999557016</v>
       </c>
       <c r="F9">
         <v>6</v>
@@ -572,27 +572,27 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>1.513138250674663</v>
+        <v>4.627076929882257</v>
       </c>
       <c r="E10">
-        <v>0.2145643168226185</v>
+        <v>0.4630630567801651</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>10</v>
@@ -601,52 +601,172 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>0.6700807647778995</v>
+        <v>0.4469640185046265</v>
       </c>
       <c r="E11">
-        <v>0.5724742187603316</v>
+        <v>0.8143625186774586</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>0.3548748385436421</v>
+        <v>4.525355616239843</v>
       </c>
       <c r="E12">
-        <v>0.7856917824606827</v>
+        <v>0.4764981284055673</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>1.1274033148126</v>
+      </c>
+      <c r="E13">
+        <v>0.3500373047470488</v>
+      </c>
+      <c r="F13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13">
-        <v>1.153251005871413</v>
-      </c>
-      <c r="E13">
-        <v>0.3301822335286443</v>
-      </c>
-      <c r="F13">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
+        <v>4.120829789765553</v>
+      </c>
+      <c r="E14">
+        <v>0.2487088232128451</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15">
+        <v>1.479304572695551</v>
+      </c>
+      <c r="E15">
+        <v>0.2235873768301785</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>0.6779462446001556</v>
+      </c>
+      <c r="E16">
+        <v>0.8783785435812842</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>0.4227304635702017</v>
+      </c>
+      <c r="E17">
+        <v>0.737141848951985</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>1.210081104032919</v>
+      </c>
+      <c r="E18">
+        <v>0.7505874758736257</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19">
+        <v>0.3548063510609488</v>
+      </c>
+      <c r="E19">
+        <v>0.7857412166024559</v>
+      </c>
+      <c r="F19">
         <v>4</v>
       </c>
     </row>

--- a/out/thesis/tables/group_tests.xlsx
+++ b/out/thesis/tables/group_tests.xlsx
@@ -461,13 +461,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>3.071368335854142</v>
+        <v>5.327762764161983</v>
       </c>
       <c r="E4">
-        <v>0.2153083337105105</v>
+        <v>0.1493110179186255</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -481,13 +481,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>1.90213983253222</v>
+        <v>1.691298759789395</v>
       </c>
       <c r="E5">
-        <v>0.155010164327115</v>
+        <v>0.1739387870455191</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -581,10 +581,10 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>4.627076929882257</v>
+        <v>6.814818130719988</v>
       </c>
       <c r="E10">
-        <v>0.4630630567801651</v>
+        <v>0.2347808268237283</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -601,10 +601,10 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>0.4469640185046265</v>
+        <v>1.646076585889095</v>
       </c>
       <c r="E11">
-        <v>0.8143625186774586</v>
+        <v>0.1560918867022053</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -701,10 +701,10 @@
         <v>12</v>
       </c>
       <c r="D16">
-        <v>0.6779462446001556</v>
+        <v>1.190196475137841</v>
       </c>
       <c r="E16">
-        <v>0.8783785435812842</v>
+        <v>0.7553565495454349</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -721,10 +721,10 @@
         <v>13</v>
       </c>
       <c r="D17">
-        <v>0.4227304635702017</v>
+        <v>0.3566901811185164</v>
       </c>
       <c r="E17">
-        <v>0.737141848951985</v>
+        <v>0.7844008225451772</v>
       </c>
       <c r="F17">
         <v>4</v>

--- a/out/thesis/tables/group_tests.xlsx
+++ b/out/thesis/tables/group_tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="15">
   <si>
     <t>group_variable</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>RUNUP_PRE_30_5</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_120</t>
   </si>
   <si>
     <t>kruskal_wallis</t>
@@ -387,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -418,7 +421,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>6.824139021857735</v>
@@ -438,7 +441,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>3.04573876599705</v>
@@ -458,7 +461,7 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4">
         <v>5.327762764161983</v>
@@ -478,7 +481,7 @@
         <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>1.691298759789395</v>
@@ -498,7 +501,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>2.15659883792379</v>
@@ -518,7 +521,7 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>0.3752196583069287</v>
@@ -532,42 +535,42 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8">
-        <v>4.833385244255167</v>
+        <v>2.178868352342995</v>
       </c>
       <c r="E8">
-        <v>0.4365508082721775</v>
+        <v>0.5361226315908982</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9">
-        <v>1.130635936208173</v>
+        <v>0.7670695341703007</v>
       </c>
       <c r="E9">
-        <v>0.3482991999557016</v>
+        <v>0.5258630422819227</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -575,16 +578,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>6.814818130719988</v>
+        <v>4.833385244255167</v>
       </c>
       <c r="E10">
-        <v>0.2347808268237283</v>
+        <v>0.4365508082721775</v>
       </c>
       <c r="F10">
         <v>6</v>
@@ -595,16 +598,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11">
-        <v>1.646076585889095</v>
+        <v>1.130635936208173</v>
       </c>
       <c r="E11">
-        <v>0.1560918867022053</v>
+        <v>0.3482991999557016</v>
       </c>
       <c r="F11">
         <v>6</v>
@@ -615,16 +618,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>4.525355616239843</v>
+        <v>6.814818130719988</v>
       </c>
       <c r="E12">
-        <v>0.4764981284055673</v>
+        <v>0.2347808268237283</v>
       </c>
       <c r="F12">
         <v>6</v>
@@ -635,16 +638,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>1.1274033148126</v>
+        <v>1.646076585889095</v>
       </c>
       <c r="E13">
-        <v>0.3500373047470488</v>
+        <v>0.1560918867022053</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -652,82 +655,82 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14">
-        <v>4.120829789765553</v>
+        <v>4.525355616239843</v>
       </c>
       <c r="E14">
-        <v>0.2487088232128451</v>
+        <v>0.4764981284055673</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15">
-        <v>1.479304572695551</v>
+        <v>1.1274033148126</v>
       </c>
       <c r="E15">
-        <v>0.2235873768301785</v>
+        <v>0.3500373047470488</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16">
-        <v>1.190196475137841</v>
+        <v>7.020209593309024</v>
       </c>
       <c r="E16">
-        <v>0.7553565495454349</v>
+        <v>0.1348240873534809</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17">
-        <v>0.3566901811185164</v>
+        <v>1.262047075414652</v>
       </c>
       <c r="E17">
-        <v>0.7844008225451772</v>
+        <v>0.3254123363598382</v>
       </c>
       <c r="F17">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -735,16 +738,16 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18">
-        <v>1.210081104032919</v>
+        <v>4.120829789765553</v>
       </c>
       <c r="E18">
-        <v>0.7505874758736257</v>
+        <v>0.2487088232128451</v>
       </c>
       <c r="F18">
         <v>4</v>
@@ -755,18 +758,138 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19">
+        <v>1.479304572695551</v>
+      </c>
+      <c r="E19">
+        <v>0.2235873768301785</v>
+      </c>
+      <c r="F19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20">
+        <v>1.190196475137841</v>
+      </c>
+      <c r="E20">
+        <v>0.7553565495454349</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>0.3566901811185164</v>
+      </c>
+      <c r="E21">
+        <v>0.7844008225451772</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
         <v>11</v>
       </c>
-      <c r="C19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19">
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22">
+        <v>1.210081104032919</v>
+      </c>
+      <c r="E22">
+        <v>0.7505874758736257</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23">
         <v>0.3548063510609488</v>
       </c>
-      <c r="E19">
+      <c r="E23">
         <v>0.7857412166024559</v>
       </c>
-      <c r="F19">
+      <c r="F23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24">
+        <v>3.866111836379452</v>
+      </c>
+      <c r="E24">
+        <v>0.2762892999070407</v>
+      </c>
+      <c r="F24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25">
+        <v>1.038780208855081</v>
+      </c>
+      <c r="E25">
+        <v>0.3968643592579329</v>
+      </c>
+      <c r="F25">
         <v>4</v>
       </c>
     </row>
